--- a/kursovoy-viv/Raschet_VV_variant3.xlsx
+++ b/kursovoy-viv/Raschet_VV_variant3.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="230">
   <si>
     <t xml:space="preserve">Расчёт систем внутреннего водопровода В1 и канализации К1 жилого здания — курсовой проект, вариант 3 (НИУ МГСУ, кафедра «Водоснабжение и водоотведение»)</t>
   </si>
@@ -495,6 +495,12 @@
   </si>
   <si>
     <t xml:space="preserve">Подача Q = q^tot, м³/ч</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Принятая установка (1 рабочий + 1 резервный)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grundfos CR 10-7: Q_ном = 10 м³/ч, H_ном = 57,2 м, 7 ступеней, 3 кВт</t>
   </si>
   <si>
     <t xml:space="preserve">Гидростатический напор у нижнего прибора этажа (смеситель ванны, 0,8 м) — п. 8.22: более 45 м → регулятор давления</t>
@@ -1409,12 +1415,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>1</v>
@@ -2056,24 +2062,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>127</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2294,7 +2300,7 @@
     </row>
     <row r="15" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -2326,7 +2332,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2337,10 +2343,10 @@
         <v>116</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>116</v>
@@ -2486,7 +2492,7 @@
     </row>
     <row r="13" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -2514,12 +2520,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B3" s="28" t="n">
         <f aca="false">К1!I12/1000</f>
@@ -2569,7 +2575,7 @@
     </row>
     <row r="5" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B5" s="34" t="str">
         <f aca="false">К1!A12</f>
@@ -6798,20 +6804,29 @@
         <v>9.3008</v>
       </c>
     </row>
+    <row r="31" customFormat="false" ht="25.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D31" s="8"/>
+    </row>
     <row r="32" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6958,6 +6973,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C31:D31"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -6986,23 +7004,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>56</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>65</v>
@@ -7011,21 +7029,21 @@
         <v>114</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>44</v>
@@ -7059,7 +7077,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>88</v>
@@ -7093,32 +7111,32 @@
     </row>
     <row r="8" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B9" s="21" t="n">
         <f aca="false">Расходы!O4</f>
         <v>0.0367626262626263</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D9" s="13" t="n">
         <f aca="false">Расходы!H4</f>
         <v>300</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>1.1</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.014</v>
@@ -7144,42 +7162,42 @@
         <v>70</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>119</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B12" s="7" t="n">
         <v>15.3</v>
@@ -7243,7 +7261,7 @@
     </row>
     <row r="13" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>11.85</v>
@@ -7307,7 +7325,7 @@
     </row>
     <row r="14" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B14" s="7" t="n">
         <v>22.5</v>
@@ -7371,7 +7389,7 @@
     </row>
     <row r="15" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B15" s="7" t="n">
         <v>9.8</v>
@@ -7435,7 +7453,7 @@
     </row>
     <row r="16" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B16" s="7" t="n">
         <v>6.2</v>
@@ -7499,17 +7517,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B21" s="7" t="n">
         <v>101</v>
@@ -7517,7 +7535,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B22" s="29" t="n">
         <v>-2</v>
@@ -7525,7 +7543,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B23" s="16" t="n">
         <f aca="false">B21+B22</f>
@@ -7534,7 +7552,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B24" s="6" t="n">
         <v>5</v>
@@ -7542,7 +7560,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B25" s="16" t="n">
         <f aca="false">B23-J13*B24</f>
@@ -7551,7 +7569,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B26" s="16" t="n">
         <f aca="false">B25+I13/1000-I14/1000</f>
@@ -7560,32 +7578,32 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="30" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B30" s="7" t="n">
         <v>100.7</v>
@@ -7609,7 +7627,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="30" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B31" s="7" t="n">
         <v>100.55</v>
@@ -7633,7 +7651,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="30" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B32" s="7" t="n">
         <v>100.4</v>
@@ -7657,7 +7675,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="30" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B33" s="7" t="n">
         <v>100.3</v>
@@ -7681,7 +7699,7 @@
     </row>
     <row r="35" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B35" s="7" t="n">
         <v>97.8</v>
@@ -7689,7 +7707,7 @@
     </row>
     <row r="36" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B36" s="16" t="n">
         <f aca="false">C33-(B35+0.4)</f>
@@ -7722,12 +7740,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>43</v>
@@ -7748,7 +7766,7 @@
         <v>48</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>50</v>
@@ -7759,7 +7777,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B3" s="31" t="n">
         <v>70</v>
@@ -7791,7 +7809,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B4" s="31" t="n">
         <v>110</v>
@@ -7823,7 +7841,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B5" s="31" t="n">
         <v>120</v>
@@ -7855,7 +7873,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B6" s="31" t="n">
         <v>130</v>
@@ -7887,7 +7905,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B7" s="31" t="n">
         <v>160</v>
@@ -7973,12 +7991,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9862,7 +9880,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/kursovoy-viv/Raschet_VV_variant3.xlsx
+++ b/kursovoy-viv/Raschet_VV_variant3.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="237">
   <si>
     <t xml:space="preserve">Расчёт систем внутреннего водопровода В1 и канализации К1 жилого здания — курсовой проект, вариант 3 (НИУ МГСУ, кафедра «Водоснабжение и водоотведение»)</t>
   </si>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">Принятая установка (1 рабочий + 1 резервный)</t>
   </si>
   <si>
-    <t xml:space="preserve">Grundfos CR 10-7: Q_ном = 10 м³/ч, H_ном = 57,2 м, 7 ступеней, 3 кВт</t>
+    <t xml:space="preserve">Grundfos CR 10-7: 7 ступеней, 3 кВт, 3×400 В (характеристика — ниже)</t>
   </si>
   <si>
     <t xml:space="preserve">Гидростатический напор у нижнего прибора этажа (смеситель ванны, 0,8 м) — п. 8.22: более 45 м → регулятор давления</t>
@@ -513,6 +513,27 @@
   </si>
   <si>
     <t xml:space="preserve">Регулятор давления</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рабочая точка насоса Grundfos CR 10-7 при подаче Q (по характеристике изготовителя, рис. 1.1 ПЗ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Напор насоса при Q по кривой H(Q), м</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Запас напора над H_нас, %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КПД насоса, %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мощность на валу P2, кВт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Потребляемая мощность P1, кВт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Требуемый кавитационный запас NPSH, м</t>
   </si>
   <si>
     <t xml:space="preserve">Канализация К1: стояки, горизонтальные участки, отметки дворовой сети</t>
@@ -907,7 +928,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1025,6 +1046,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1415,12 +1440,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>1</v>
@@ -2062,24 +2087,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>127</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,13 +2114,13 @@
       <c r="B3" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="C3" s="32" t="n">
+      <c r="C3" s="33" t="n">
         <v>14.5</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E3" s="33" t="b">
+      <c r="E3" s="34" t="b">
         <f aca="false">AND(B3&gt;=Напор!$C$5,C3*Напор!$C$6^2&lt;=D3)</f>
         <v>0</v>
       </c>
@@ -2107,13 +2132,13 @@
       <c r="B4" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="32" t="n">
+      <c r="C4" s="33" t="n">
         <v>5.18</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="33" t="b">
+      <c r="E4" s="34" t="b">
         <f aca="false">AND(B4&gt;=Напор!$C$5,C4*Напор!$C$6^2&lt;=D4)</f>
         <v>0</v>
       </c>
@@ -2125,13 +2150,13 @@
       <c r="B5" s="6" t="n">
         <v>2.8</v>
       </c>
-      <c r="C5" s="32" t="n">
+      <c r="C5" s="33" t="n">
         <v>2.64</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="33" t="b">
+      <c r="E5" s="34" t="b">
         <f aca="false">AND(B5&gt;=Напор!$C$5,C5*Напор!$C$6^2&lt;=D5)</f>
         <v>0</v>
       </c>
@@ -2143,13 +2168,13 @@
       <c r="B6" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="32" t="n">
+      <c r="C6" s="33" t="n">
         <v>1.3</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="33" t="b">
+      <c r="E6" s="34" t="b">
         <f aca="false">AND(B6&gt;=Напор!$C$5,C6*Напор!$C$6^2&lt;=D6)</f>
         <v>0</v>
       </c>
@@ -2161,13 +2186,13 @@
       <c r="B7" s="6" t="n">
         <v>6.4</v>
       </c>
-      <c r="C7" s="32" t="n">
+      <c r="C7" s="33" t="n">
         <v>0.5</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="33" t="b">
+      <c r="E7" s="34" t="b">
         <f aca="false">AND(B7&gt;=Напор!$C$5,C7*Напор!$C$6^2&lt;=D7)</f>
         <v>1</v>
       </c>
@@ -2179,13 +2204,13 @@
       <c r="B8" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="C8" s="32" t="n">
+      <c r="C8" s="33" t="n">
         <v>0.143</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="E8" s="33" t="b">
+      <c r="E8" s="34" t="b">
         <f aca="false">AND(B8&gt;=Напор!$C$5,C8*Напор!$C$6^2&lt;=D8)</f>
         <v>1</v>
       </c>
@@ -2197,13 +2222,13 @@
       <c r="B9" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="33" t="n">
         <v>0.0081</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="E9" s="33" t="b">
+      <c r="E9" s="34" t="b">
         <f aca="false">AND(B9&gt;=Напор!$C$5,C9*Напор!$C$6^2&lt;=D9)</f>
         <v>1</v>
       </c>
@@ -2215,13 +2240,13 @@
       <c r="B10" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="33" t="n">
         <v>0.00264</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="E10" s="33" t="b">
+      <c r="E10" s="34" t="b">
         <f aca="false">AND(B10&gt;=Напор!$C$5,C10*Напор!$C$6^2&lt;=D10)</f>
         <v>1</v>
       </c>
@@ -2233,13 +2258,13 @@
       <c r="B11" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="33" t="n">
         <v>0.000766</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="E11" s="33" t="b">
+      <c r="E11" s="34" t="b">
         <f aca="false">AND(B11&gt;=Напор!$C$5,C11*Напор!$C$6^2&lt;=D11)</f>
         <v>1</v>
       </c>
@@ -2251,13 +2276,13 @@
       <c r="B12" s="6" t="n">
         <v>140</v>
       </c>
-      <c r="C12" s="32" t="n">
+      <c r="C12" s="33" t="n">
         <v>0.00013</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="E12" s="33" t="b">
+      <c r="E12" s="34" t="b">
         <f aca="false">AND(B12&gt;=Напор!$C$5,C12*Напор!$C$6^2&lt;=D12)</f>
         <v>1</v>
       </c>
@@ -2269,13 +2294,13 @@
       <c r="B13" s="6" t="n">
         <v>210</v>
       </c>
-      <c r="C13" s="32" t="n">
+      <c r="C13" s="33" t="n">
         <v>3.5E-005</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="E13" s="33" t="b">
+      <c r="E13" s="34" t="b">
         <f aca="false">AND(B13&gt;=Напор!$C$5,C13*Напор!$C$6^2&lt;=D13)</f>
         <v>1</v>
       </c>
@@ -2287,20 +2312,20 @@
       <c r="B14" s="6" t="n">
         <v>380</v>
       </c>
-      <c r="C14" s="32" t="n">
+      <c r="C14" s="33" t="n">
         <v>1.8E-005</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="E14" s="33" t="b">
+      <c r="E14" s="34" t="b">
         <f aca="false">AND(B14&gt;=Напор!$C$5,C14*Напор!$C$6^2&lt;=D14)</f>
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -2332,7 +2357,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2343,10 +2368,10 @@
         <v>116</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>116</v>
@@ -2492,7 +2517,7 @@
     </row>
     <row r="13" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2520,12 +2545,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B3" s="28" t="n">
         <f aca="false">К1!I12/1000</f>
@@ -2575,25 +2600,25 @@
     </row>
     <row r="5" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B5" s="34" t="str">
+        <v>180</v>
+      </c>
+      <c r="B5" s="35" t="str">
         <f aca="false">К1!A12</f>
         <v>Ст.К1-4 – Ст.К1-3 (чугун SML)</v>
       </c>
-      <c r="C5" s="34" t="str">
+      <c r="C5" s="35" t="str">
         <f aca="false">К1!A13</f>
         <v>Ст.К1-3 – КК-1, выпуск К1-2 (чугун SML)</v>
       </c>
-      <c r="D5" s="34" t="str">
+      <c r="D5" s="35" t="str">
         <f aca="false">К1!A14</f>
         <v>КК-1 – КК-2 (ПЭ гофр. Ø160)</v>
       </c>
-      <c r="E5" s="34" t="str">
+      <c r="E5" s="35" t="str">
         <f aca="false">К1!A15</f>
         <v>КК-2 – ККК (ПЭ гофр. Ø160)</v>
       </c>
-      <c r="F5" s="34" t="str">
+      <c r="F5" s="35" t="str">
         <f aca="false">К1!A16</f>
         <v>ККК – ГКК (ПЭ гофр. Ø160)</v>
       </c>
@@ -6581,7 +6606,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -6970,6 +6995,60 @@
       <c r="D44" s="25" t="str">
         <f aca="false">IF(C44&gt;45,"нужен","не нужен")</f>
         <v>не нужен</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C48" s="30" t="n">
+        <f aca="false">(C47/C29-1)*100</f>
+        <v>8.23428550153904</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
@@ -7004,23 +7083,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>56</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>65</v>
@@ -7029,21 +7108,21 @@
         <v>114</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>44</v>
@@ -7077,7 +7156,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>88</v>
@@ -7111,32 +7190,32 @@
     </row>
     <row r="8" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B9" s="21" t="n">
         <f aca="false">Расходы!O4</f>
         <v>0.0367626262626263</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D9" s="13" t="n">
         <f aca="false">Расходы!H4</f>
         <v>300</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>1.1</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.014</v>
@@ -7162,42 +7241,42 @@
         <v>70</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>119</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B12" s="7" t="n">
         <v>15.3</v>
@@ -7261,7 +7340,7 @@
     </row>
     <row r="13" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>11.85</v>
@@ -7325,7 +7404,7 @@
     </row>
     <row r="14" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B14" s="7" t="n">
         <v>22.5</v>
@@ -7389,7 +7468,7 @@
     </row>
     <row r="15" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B15" s="7" t="n">
         <v>9.8</v>
@@ -7453,7 +7532,7 @@
     </row>
     <row r="16" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B16" s="7" t="n">
         <v>6.2</v>
@@ -7517,17 +7596,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B21" s="7" t="n">
         <v>101</v>
@@ -7535,7 +7614,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B22" s="29" t="n">
         <v>-2</v>
@@ -7543,7 +7622,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B23" s="16" t="n">
         <f aca="false">B21+B22</f>
@@ -7552,7 +7631,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B24" s="6" t="n">
         <v>5</v>
@@ -7560,7 +7639,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B25" s="16" t="n">
         <f aca="false">B23-J13*B24</f>
@@ -7569,7 +7648,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B26" s="16" t="n">
         <f aca="false">B25+I13/1000-I14/1000</f>
@@ -7578,32 +7657,32 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="30" t="s">
-        <v>199</v>
+      <c r="A30" s="31" t="s">
+        <v>206</v>
       </c>
       <c r="B30" s="7" t="n">
         <v>100.7</v>
@@ -7626,8 +7705,8 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="30" t="s">
-        <v>200</v>
+      <c r="A31" s="31" t="s">
+        <v>207</v>
       </c>
       <c r="B31" s="7" t="n">
         <v>100.55</v>
@@ -7650,8 +7729,8 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="30" t="s">
-        <v>201</v>
+      <c r="A32" s="31" t="s">
+        <v>208</v>
       </c>
       <c r="B32" s="7" t="n">
         <v>100.4</v>
@@ -7674,8 +7753,8 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="30" t="s">
-        <v>202</v>
+      <c r="A33" s="31" t="s">
+        <v>209</v>
       </c>
       <c r="B33" s="7" t="n">
         <v>100.3</v>
@@ -7699,7 +7778,7 @@
     </row>
     <row r="35" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B35" s="7" t="n">
         <v>97.8</v>
@@ -7707,7 +7786,7 @@
     </row>
     <row r="36" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B36" s="16" t="n">
         <f aca="false">C33-(B35+0.4)</f>
@@ -7740,12 +7819,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>43</v>
@@ -7766,7 +7845,7 @@
         <v>48</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>50</v>
@@ -7777,161 +7856,161 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="B3" s="31" t="n">
+        <v>215</v>
+      </c>
+      <c r="B3" s="32" t="n">
         <v>70</v>
       </c>
-      <c r="C3" s="31" t="n">
+      <c r="C3" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="31" t="n">
+      <c r="D3" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="E3" s="31" t="n">
+      <c r="E3" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="31" t="n">
+      <c r="F3" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="G3" s="31" t="n">
+      <c r="G3" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="H3" s="31" t="n">
+      <c r="H3" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="I3" s="31" t="n">
+      <c r="I3" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="J3" s="31" t="n">
+      <c r="J3" s="32" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="B4" s="31" t="n">
+        <v>216</v>
+      </c>
+      <c r="B4" s="32" t="n">
         <v>110</v>
       </c>
-      <c r="C4" s="31" t="n">
+      <c r="C4" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="31" t="n">
+      <c r="D4" s="32" t="n">
         <v>8.1</v>
       </c>
-      <c r="E4" s="31" t="n">
+      <c r="E4" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="31" t="n">
+      <c r="F4" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="G4" s="31" t="n">
+      <c r="G4" s="32" t="n">
         <v>300</v>
       </c>
-      <c r="H4" s="31" t="n">
+      <c r="H4" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="I4" s="31" t="n">
+      <c r="I4" s="32" t="n">
         <v>300</v>
       </c>
-      <c r="J4" s="31" t="n">
+      <c r="J4" s="32" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="B5" s="31" t="n">
+        <v>217</v>
+      </c>
+      <c r="B5" s="32" t="n">
         <v>120</v>
       </c>
-      <c r="C5" s="31" t="n">
+      <c r="C5" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="31" t="n">
+      <c r="D5" s="32" t="n">
         <v>8.7</v>
       </c>
-      <c r="E5" s="31" t="n">
+      <c r="E5" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="31" t="n">
+      <c r="F5" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="G5" s="31" t="n">
+      <c r="G5" s="32" t="n">
         <v>300</v>
       </c>
-      <c r="H5" s="31" t="n">
+      <c r="H5" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="I5" s="31" t="n">
+      <c r="I5" s="32" t="n">
         <v>300</v>
       </c>
-      <c r="J5" s="31" t="n">
+      <c r="J5" s="32" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="B6" s="31" t="n">
+        <v>218</v>
+      </c>
+      <c r="B6" s="32" t="n">
         <v>130</v>
       </c>
-      <c r="C6" s="31" t="n">
+      <c r="C6" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="D6" s="31" t="n">
+      <c r="D6" s="32" t="n">
         <v>8.2</v>
       </c>
-      <c r="E6" s="31" t="n">
+      <c r="E6" s="32" t="n">
         <v>4.5</v>
       </c>
-      <c r="F6" s="31" t="n">
+      <c r="F6" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="G6" s="31" t="n">
+      <c r="G6" s="32" t="n">
         <v>100</v>
       </c>
-      <c r="H6" s="31" t="n">
+      <c r="H6" s="32" t="n">
         <v>0.14</v>
       </c>
-      <c r="I6" s="31" t="n">
+      <c r="I6" s="32" t="n">
         <v>60</v>
       </c>
-      <c r="J6" s="31" t="n">
+      <c r="J6" s="32" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="B7" s="31" t="n">
+        <v>219</v>
+      </c>
+      <c r="B7" s="32" t="n">
         <v>160</v>
       </c>
-      <c r="C7" s="31" t="n">
+      <c r="C7" s="32" t="n">
         <v>65</v>
       </c>
-      <c r="D7" s="31" t="n">
+      <c r="D7" s="32" t="n">
         <v>10.3</v>
       </c>
-      <c r="E7" s="31" t="n">
+      <c r="E7" s="32" t="n">
         <v>5.7</v>
       </c>
-      <c r="F7" s="31" t="n">
+      <c r="F7" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="G7" s="31" t="n">
+      <c r="G7" s="32" t="n">
         <v>300</v>
       </c>
-      <c r="H7" s="31" t="n">
+      <c r="H7" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="I7" s="31" t="n">
+      <c r="I7" s="32" t="n">
         <v>200</v>
       </c>
-      <c r="J7" s="31" t="n">
+      <c r="J7" s="32" t="n">
         <v>24</v>
       </c>
     </row>
@@ -7939,31 +8018,31 @@
       <c r="A8" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="32" t="n">
         <v>180</v>
       </c>
-      <c r="C8" s="31" t="n">
+      <c r="C8" s="32" t="n">
         <v>70</v>
       </c>
-      <c r="D8" s="31" t="n">
+      <c r="D8" s="32" t="n">
         <v>11.6</v>
       </c>
-      <c r="E8" s="31" t="n">
+      <c r="E8" s="32" t="n">
         <v>6.5</v>
       </c>
-      <c r="F8" s="31" t="n">
+      <c r="F8" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="G8" s="31" t="n">
+      <c r="G8" s="32" t="n">
         <v>300</v>
       </c>
-      <c r="H8" s="31" t="n">
+      <c r="H8" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="I8" s="31" t="n">
+      <c r="I8" s="32" t="n">
         <v>200</v>
       </c>
-      <c r="J8" s="31" t="n">
+      <c r="J8" s="32" t="n">
         <v>24</v>
       </c>
     </row>
@@ -7991,12 +8070,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9880,7 +9959,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
